--- a/slide_classification/TCGA_Results/Caption_based_aggregation/Virchow2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation/Virchow2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8932038834951457</v>
+        <v>0.883495145631068</v>
       </c>
       <c r="C14" t="n">
         <v>0.865979381443299</v>
@@ -761,10 +761,10 @@
         <v>0.8392857142857143</v>
       </c>
       <c r="E14" t="n">
-        <v>0.900990099009901</v>
+        <v>0.8514851485148515</v>
       </c>
       <c r="F14" t="n">
-        <v>0.874864769558515</v>
+        <v>0.8600613474687332</v>
       </c>
     </row>
     <row r="15">
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6609848484848485</v>
+        <v>0.6829545454545455</v>
       </c>
       <c r="C15" t="n">
         <v>0.5</v>
@@ -783,10 +783,10 @@
         <v>0.6478260869565218</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6914794007490637</v>
+        <v>0.6273408239700374</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6250725840476086</v>
+        <v>0.6145303640952762</v>
       </c>
     </row>
     <row r="16">
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7083655083655084</v>
+        <v>0.717032967032967</v>
       </c>
       <c r="C16" t="n">
         <v>0.4640883977900552</v>
@@ -805,10 +805,10 @@
         <v>0.671875</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7225274725274725</v>
+        <v>0.6320136021374787</v>
       </c>
       <c r="F16" t="n">
-        <v>0.641714094670759</v>
+        <v>0.6212524917401252</v>
       </c>
     </row>
     <row r="17">
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8729167447614049</v>
+        <v>0.8708524485223516</v>
       </c>
       <c r="C17" t="n">
         <v>0.8037819673064874</v>
@@ -827,10 +827,10 @@
         <v>0.8225446428571429</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8921771298008921</v>
+        <v>0.8486714107407827</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8478551211814818</v>
+        <v>0.8364626173566911</v>
       </c>
     </row>
     <row r="18">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7359848484848486</v>
+        <v>0.7553030303030303</v>
       </c>
       <c r="C18" t="n">
         <v>0.6469780219780219</v>
@@ -849,10 +849,10 @@
         <v>0.7046195652173912</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7467228464419475</v>
+        <v>0.6896067415730338</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7085763205305524</v>
+        <v>0.6991268397678694</v>
       </c>
     </row>
     <row r="19">
@@ -863,7 +863,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[[87, 1], [10, 5]]</t>
+          <t>[[85, 3], [9, 6]]</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[[86, 3], [7, 5]]</t>
+          <t>[[82, 7], [8, 4]]</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[[86, 2], [11, 4]]</t>
+          <t>[[84, 4], [11, 4]]</t>
         </is>
       </c>
     </row>
@@ -1406,38 +1406,38 @@
         <v>413</v>
       </c>
       <c r="F4" t="n">
-        <v>0.874864769558515</v>
+        <v>0.8600613474687332</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02430882162398667</v>
+        <v>0.01650260695382005</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6250725840476086</v>
+        <v>0.6145303640952762</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07392636406655431</v>
+        <v>0.06905031849589552</v>
       </c>
       <c r="J4" t="n">
-        <v>0.641714094670759</v>
+        <v>0.6212524917401252</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1042038643606316</v>
+        <v>0.09559405278830664</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8478551211814818</v>
+        <v>0.8364626173566911</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03597078199739548</v>
+        <v>0.02546296342421685</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7085763205305524</v>
+        <v>0.6991268397678694</v>
       </c>
       <c r="O4" t="n">
-        <v>0.03878269956083861</v>
+        <v>0.03871713407015216</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>[[86, 2], [11, 4]]</t>
+          <t>[[84, 4], [11, 4]]</t>
         </is>
       </c>
     </row>

--- a/slide_classification/TCGA_Results/Caption_based_aggregation/Virchow2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation/Virchow2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -610,19 +610,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8446601941747572</v>
+        <v>0.7961165048543689</v>
       </c>
       <c r="C8" t="n">
         <v>0.8247422680412371</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8035714285714286</v>
+        <v>0.8214285714285714</v>
       </c>
       <c r="E8" t="n">
         <v>0.8514851485148515</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8311147598255686</v>
+        <v>0.8234431232097572</v>
       </c>
     </row>
     <row r="9">
@@ -632,19 +632,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7984848484848485</v>
+        <v>0.7147727272727273</v>
       </c>
       <c r="C9" t="n">
         <v>0.7687728937728937</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7630434782608695</v>
+        <v>0.8130434782608695</v>
       </c>
       <c r="E9" t="n">
         <v>0.7715355805243446</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7754592002607391</v>
+        <v>0.7670311699577088</v>
       </c>
     </row>
     <row r="10">
@@ -654,19 +654,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7418546365914787</v>
+        <v>0.6678949792722249</v>
       </c>
       <c r="C10" t="n">
         <v>0.7036837376460018</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7167816091954023</v>
+        <v>0.7495527728085868</v>
       </c>
       <c r="E10" t="n">
         <v>0.7142048670062252</v>
       </c>
       <c r="F10" t="n">
-        <v>0.719131212609777</v>
+        <v>0.7088340891832596</v>
       </c>
     </row>
     <row r="11">
@@ -676,19 +676,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8573131858773148</v>
+        <v>0.814147656889358</v>
       </c>
       <c r="C11" t="n">
         <v>0.8423152805179649</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8175697865353039</v>
+        <v>0.8358037311525683</v>
       </c>
       <c r="E11" t="n">
         <v>0.865213176665714</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8456028573990744</v>
+        <v>0.8393699613064012</v>
       </c>
     </row>
     <row r="12">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9037878787878788</v>
+        <v>0.8825757575757576</v>
       </c>
       <c r="C12" t="n">
         <v>0.8379120879120879</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8679347826086956</v>
+        <v>0.870108695652174</v>
       </c>
       <c r="E12" t="n">
         <v>0.8295880149812734</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8598056910724839</v>
+        <v>0.8550461390303232</v>
       </c>
     </row>
     <row r="13">
@@ -721,7 +721,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[[76, 12], [4, 11]]</t>
+          <t>[[73, 15], [6, 9]]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[[76, 16], [6, 14]]</t>
+          <t>[[76, 16], [4, 16]]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[[75, 13], [4, 10]]</t>
+          <t>[[74, 14], [4, 10]]</t>
         </is>
       </c>
     </row>
@@ -1348,38 +1348,38 @@
         <v>413</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8311147598255686</v>
+        <v>0.8234431232097572</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01869274775934039</v>
+        <v>0.01961406032751015</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7754592002607391</v>
+        <v>0.7670311699577088</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01364214165008289</v>
+        <v>0.03489771003821672</v>
       </c>
       <c r="J3" t="n">
-        <v>0.719131212609777</v>
+        <v>0.7088340891832596</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01400685544134649</v>
+        <v>0.02910924806598525</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8456028573990744</v>
+        <v>0.8393699613064012</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01815459747977222</v>
+        <v>0.01820322308673611</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8598056910724839</v>
+        <v>0.8550461390303232</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02912452906543965</v>
+        <v>0.02194568463880023</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[[75, 13], [4, 10]]</t>
+          <t>[[74, 14], [4, 10]]</t>
         </is>
       </c>
     </row>
